--- a/SCH-STH/Impact assessments/Mali/2025/ml_sch_sth_impact_2501_2_child.xlsx
+++ b/SCH-STH/Impact assessments/Mali/2025/ml_sch_sth_impact_2501_2_child.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\SCH-STH\Impact assessments\Mali\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102FE37D-B55A-4AFA-B079-1A21C1FACDD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3710B4C-E8C7-4682-B5C2-4990079139DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -476,9 +476,6 @@
     <t>Code de l'Opérateur</t>
   </si>
   <si>
-    <t>Sélectionner le sous-district</t>
-  </si>
-  <si>
     <t xml:space="preserve">${p_consent} = 'A.donne' </t>
   </si>
   <si>
@@ -488,115 +485,118 @@
     <t>p_site_id</t>
   </si>
   <si>
+    <t>p_code_id</t>
+  </si>
+  <si>
+    <t>read_only</t>
+  </si>
+  <si>
+    <t>bind::db_get</t>
+  </si>
+  <si>
+    <t>bind::db_filter_by_col_1</t>
+  </si>
+  <si>
+    <t>bind::db_filter_by_col_2</t>
+  </si>
+  <si>
+    <t>bind::db_filter_by_col_3</t>
+  </si>
+  <si>
+    <t>col_1</t>
+  </si>
+  <si>
+    <t>col_2</t>
+  </si>
+  <si>
+    <t>col_3</t>
+  </si>
+  <si>
+    <t>col_4</t>
+  </si>
+  <si>
+    <t>${p_district}</t>
+  </si>
+  <si>
+    <t>${p_subdistrict}</t>
+  </si>
+  <si>
+    <t>${p_site}</t>
+  </si>
+  <si>
+    <t>calculate</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>begin repeat</t>
+  </si>
+  <si>
+    <t>Enrôlement</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>position(..)</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>join(' ', ${p_code_id})</t>
+  </si>
+  <si>
+    <t>if (${C2} = 1,'',substring-after(${C1},${p_code_id}))</t>
+  </si>
+  <si>
+    <t>end repeat</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>Sélectionner l'aire de santé</t>
+  </si>
+  <si>
+    <t>Veuillez enregistrer le code unique de l’enfant et des échantillons de labo </t>
+  </si>
+  <si>
+    <t>ml_sch_sth_impact_2501_2_child_v2_1</t>
+  </si>
+  <si>
+    <t>(2025 Jan) - 2. SCH/STH – Enrôlement V2.1</t>
+  </si>
+  <si>
+    <t>ml_ia_e_250121</t>
+  </si>
+  <si>
+    <t>Veuillez entrer le code séquentiel</t>
+  </si>
+  <si>
+    <t>Répétez le code séquentiel</t>
+  </si>
+  <si>
+    <t>Le code répété doit être le même</t>
+  </si>
+  <si>
+    <t>not(selected(${C3}, ${p_code_id}))</t>
+  </si>
+  <si>
+    <t>concat(${p_recorder} , '_',  ${p_site_id} , '_',  ${p_sequential_code})</t>
+  </si>
+  <si>
     <t>p_sequential_code</t>
   </si>
   <si>
-    <t>Veuillez entrer le code séquentiel</t>
-  </si>
-  <si>
     <t>p_sequential_code2</t>
   </si>
   <si>
-    <t>Répétez le code séquentiel</t>
-  </si>
-  <si>
     <t>. = ${p_sequential_code}</t>
   </si>
   <si>
-    <t>Le code répété doit être le même</t>
-  </si>
-  <si>
-    <t>p_code_id</t>
-  </si>
-  <si>
-    <t>Veuillez enregistrer ce code unique de l’enfant dans les registres et les échantillons de labo </t>
-  </si>
-  <si>
-    <t>read_only</t>
-  </si>
-  <si>
-    <t>ml_sch_sth_impact_2501_2_child</t>
-  </si>
-  <si>
-    <t>(2025 Jan) - 2. SCH/STH – Enrôlement</t>
-  </si>
-  <si>
-    <t>bind::db_get</t>
-  </si>
-  <si>
-    <t>bind::db_filter_by_col_1</t>
-  </si>
-  <si>
-    <t>bind::db_filter_by_col_2</t>
-  </si>
-  <si>
-    <t>bind::db_filter_by_col_3</t>
-  </si>
-  <si>
-    <t>col_1</t>
-  </si>
-  <si>
-    <t>col_2</t>
-  </si>
-  <si>
-    <t>col_3</t>
-  </si>
-  <si>
-    <t>col_4</t>
-  </si>
-  <si>
-    <t>${p_district}</t>
-  </si>
-  <si>
-    <t>${p_subdistrict}</t>
-  </si>
-  <si>
-    <t>${p_site}</t>
-  </si>
-  <si>
-    <t>calculate</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>begin repeat</t>
-  </si>
-  <si>
-    <t>Enrôlement</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>position(..)</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>ml_ia_e_2501</t>
-  </si>
-  <si>
-    <t>join(' ', ${p_code_id})</t>
-  </si>
-  <si>
-    <t>if (${C2} = 1,'',substring-after(${C1},${p_code_id}))</t>
-  </si>
-  <si>
     <t>Cet identifiant a déjà été utilisé dans ce village.</t>
-  </si>
-  <si>
-    <t>not(selected(${C3}, ${p_code_id}))</t>
-  </si>
-  <si>
-    <t>concat(${p_recorder}, '_', ${p_site_id}, '_', ${p_sequential_code})</t>
-  </si>
-  <si>
-    <t>end repeat</t>
-  </si>
-  <si>
-    <t>string</t>
   </si>
 </sst>
 </file>
@@ -805,7 +805,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -870,9 +870,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -913,6 +910,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1196,15 +1199,15 @@
     <col min="3" max="3" width="47.5" style="4" customWidth="1"/>
     <col min="4" max="4" width="47.375" customWidth="1"/>
     <col min="5" max="5" width="12.625" customWidth="1"/>
-    <col min="6" max="6" width="16.875" customWidth="1"/>
+    <col min="6" max="6" width="29.625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29.5" customWidth="1"/>
     <col min="8" max="8" width="35" customWidth="1"/>
-    <col min="9" max="9" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.25" customWidth="1"/>
     <col min="10" max="10" width="9.75" customWidth="1"/>
     <col min="11" max="11" width="13.875" customWidth="1"/>
     <col min="12" max="12" width="36.625" customWidth="1"/>
-    <col min="14" max="14" width="13.75" style="31" bestFit="1" customWidth="1"/>
-    <col min="15" max="19" width="25.75" style="31" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.75" style="30" bestFit="1" customWidth="1"/>
+    <col min="15" max="19" width="25.75" style="30" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" s="17" customFormat="1" ht="37.5" x14ac:dyDescent="0.3">
@@ -1244,23 +1247,23 @@
       <c r="L1" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>157</v>
-      </c>
-      <c r="N1" s="30" t="s">
-        <v>160</v>
-      </c>
-      <c r="O1" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="P1" s="30" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q1" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
+      <c r="M1" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="N1" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="O1" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="P1" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q1" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
     </row>
     <row r="2" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
@@ -1283,16 +1286,16 @@
       </c>
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
-      <c r="N2" s="31"/>
-      <c r="O2" s="31"/>
-      <c r="P2" s="31"/>
-      <c r="Q2" s="31"/>
-      <c r="R2" s="31"/>
-      <c r="S2" s="31"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
     </row>
     <row r="3" spans="1:19" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>14</v>
@@ -1311,24 +1314,24 @@
       </c>
       <c r="K3" s="9"/>
       <c r="L3" s="8"/>
-      <c r="N3" s="31" t="s">
-        <v>164</v>
-      </c>
-      <c r="O3" s="31"/>
-      <c r="P3" s="31"/>
-      <c r="Q3" s="31"/>
-      <c r="R3" s="31"/>
-      <c r="S3" s="31"/>
+      <c r="N3" s="30" t="s">
+        <v>154</v>
+      </c>
+      <c r="O3" s="30"/>
+      <c r="P3" s="30"/>
+      <c r="Q3" s="30"/>
+      <c r="R3" s="30"/>
+      <c r="S3" s="30"/>
     </row>
     <row r="4" spans="1:19" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="8"/>
@@ -1341,20 +1344,20 @@
       </c>
       <c r="K4" s="9"/>
       <c r="L4" s="8"/>
-      <c r="N4" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="O4" s="31" t="s">
-        <v>168</v>
-      </c>
-      <c r="P4" s="31"/>
-      <c r="Q4" s="31"/>
-      <c r="R4" s="31"/>
-      <c r="S4" s="31"/>
+      <c r="N4" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="O4" s="30" t="s">
+        <v>158</v>
+      </c>
+      <c r="P4" s="30"/>
+      <c r="Q4" s="30"/>
+      <c r="R4" s="30"/>
+      <c r="S4" s="30"/>
     </row>
     <row r="5" spans="1:19" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>17</v>
@@ -1373,26 +1376,26 @@
       </c>
       <c r="K5" s="9"/>
       <c r="L5" s="8"/>
-      <c r="N5" s="31" t="s">
-        <v>166</v>
-      </c>
-      <c r="O5" s="31"/>
-      <c r="P5" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q5" s="31"/>
-      <c r="R5" s="31"/>
-      <c r="S5" s="31"/>
+      <c r="N5" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="O5" s="30"/>
+      <c r="P5" s="30" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q5" s="30"/>
+      <c r="R5" s="30"/>
+      <c r="S5" s="30"/>
     </row>
     <row r="6" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>148</v>
+        <v>171</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>147</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D6" s="21"/>
       <c r="E6" s="9"/>
@@ -1405,101 +1408,101 @@
       </c>
       <c r="K6" s="9"/>
       <c r="L6" s="7"/>
-      <c r="N6" s="31" t="s">
-        <v>167</v>
-      </c>
-      <c r="O6" s="32"/>
-      <c r="P6" s="32"/>
-      <c r="Q6" s="32" t="s">
-        <v>170</v>
-      </c>
-      <c r="R6" s="32"/>
-      <c r="S6" s="32"/>
-    </row>
-    <row r="7" spans="1:19" s="33" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="34" t="s">
-        <v>171</v>
-      </c>
-      <c r="B7" s="35" t="s">
-        <v>172</v>
+      <c r="N6" s="30" t="s">
+        <v>157</v>
+      </c>
+      <c r="O6" s="31"/>
+      <c r="P6" s="31"/>
+      <c r="Q6" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="R6" s="31"/>
+      <c r="S6" s="31"/>
+    </row>
+    <row r="7" spans="1:19" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>162</v>
       </c>
       <c r="C7"/>
       <c r="D7"/>
       <c r="E7"/>
       <c r="F7"/>
       <c r="G7"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="34" t="s">
-        <v>179</v>
-      </c>
-      <c r="J7" s="34"/>
-      <c r="K7" s="34"/>
-      <c r="L7" s="34"/>
-      <c r="M7" s="34"/>
-    </row>
-    <row r="8" spans="1:19" s="33" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="36" t="s">
-        <v>173</v>
-      </c>
-      <c r="B8" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="C8" s="38" t="s">
-        <v>174</v>
-      </c>
-      <c r="D8" s="37"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="36"/>
-      <c r="K8" s="36"/>
-      <c r="L8" s="36"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="41"/>
-    </row>
-    <row r="9" spans="1:19" s="33" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="34" t="s">
-        <v>171</v>
-      </c>
-      <c r="B9" s="35" t="s">
-        <v>175</v>
+      <c r="H7" s="34"/>
+      <c r="I7" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="J7" s="33"/>
+      <c r="K7" s="33"/>
+      <c r="L7" s="33"/>
+      <c r="M7" s="33"/>
+    </row>
+    <row r="8" spans="1:19" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="35" t="s">
+        <v>163</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="D8" s="36"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="35"/>
+      <c r="N8" s="40"/>
+    </row>
+    <row r="9" spans="1:19" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>165</v>
       </c>
       <c r="C9"/>
       <c r="D9"/>
       <c r="E9"/>
       <c r="F9"/>
       <c r="G9"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="34" t="s">
-        <v>176</v>
-      </c>
-      <c r="J9" s="34"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="34"/>
-      <c r="M9" s="34"/>
-    </row>
-    <row r="10" spans="1:19" s="33" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="34" t="s">
-        <v>171</v>
-      </c>
-      <c r="B10" s="35" t="s">
-        <v>177</v>
+      <c r="H9" s="34"/>
+      <c r="I9" s="33" t="s">
+        <v>166</v>
+      </c>
+      <c r="J9" s="33"/>
+      <c r="K9" s="33"/>
+      <c r="L9" s="33"/>
+      <c r="M9" s="33"/>
+    </row>
+    <row r="10" spans="1:19" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>167</v>
       </c>
       <c r="C10"/>
       <c r="D10"/>
       <c r="E10"/>
       <c r="F10"/>
       <c r="G10"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="J10" s="34"/>
-      <c r="K10" s="34"/>
-      <c r="L10" s="34"/>
-      <c r="M10" s="34"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="J10" s="33"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="33"/>
     </row>
     <row r="11" spans="1:19" s="17" customFormat="1" ht="169.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
@@ -1520,12 +1523,12 @@
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
-      <c r="N11" s="31"/>
-      <c r="O11" s="32"/>
-      <c r="P11" s="32"/>
-      <c r="Q11" s="32"/>
-      <c r="R11" s="32"/>
-      <c r="S11" s="32"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="31"/>
+      <c r="P11" s="31"/>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="31"/>
+      <c r="S11" s="31"/>
     </row>
     <row r="12" spans="1:19" s="17" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
@@ -1550,22 +1553,22 @@
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="8"/>
-      <c r="N12" s="31"/>
-      <c r="O12" s="31"/>
-      <c r="P12" s="31"/>
-      <c r="Q12" s="31"/>
-      <c r="R12" s="31"/>
-      <c r="S12" s="32"/>
-    </row>
-    <row r="13" spans="1:19" s="17" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="N12" s="30"/>
+      <c r="O12" s="30"/>
+      <c r="P12" s="30"/>
+      <c r="Q12" s="30"/>
+      <c r="R12" s="30"/>
+      <c r="S12" s="31"/>
+    </row>
+    <row r="13" spans="1:19" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="26" t="s">
-        <v>149</v>
+      <c r="B13" s="25" t="s">
+        <v>182</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="9"/>
@@ -1574,91 +1577,93 @@
       <c r="H13" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I13" s="9"/>
+      <c r="I13" s="25"/>
       <c r="J13" s="9" t="s">
         <v>13</v>
       </c>
       <c r="K13" s="9"/>
       <c r="L13" s="9"/>
-      <c r="N13" s="33"/>
-      <c r="O13" s="33"/>
-      <c r="P13" s="33"/>
-      <c r="Q13" s="33"/>
-      <c r="R13" s="33"/>
-      <c r="S13" s="33"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="32"/>
+      <c r="P13" s="32"/>
+      <c r="Q13" s="32"/>
+      <c r="R13" s="32"/>
+      <c r="S13" s="32"/>
     </row>
     <row r="14" spans="1:19" s="17" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>151</v>
+      <c r="B14" s="25" t="s">
+        <v>183</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="9"/>
-      <c r="F14" s="8" t="s">
-        <v>153</v>
+      <c r="F14" s="42" t="s">
+        <v>184</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I14" s="9"/>
+      <c r="I14" s="25"/>
       <c r="J14" s="9" t="s">
         <v>13</v>
       </c>
       <c r="K14" s="9"/>
       <c r="L14" s="9"/>
-      <c r="N14" s="33"/>
-      <c r="O14" s="33"/>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="33"/>
-      <c r="S14" s="33"/>
-    </row>
-    <row r="15" spans="1:19" s="17" customFormat="1" ht="63" x14ac:dyDescent="0.25">
+      <c r="M14" s="27"/>
+      <c r="N14" s="32"/>
+      <c r="O14" s="32"/>
+      <c r="P14" s="32"/>
+      <c r="Q14" s="32"/>
+      <c r="R14" s="32"/>
+      <c r="S14" s="32"/>
+    </row>
+    <row r="15" spans="1:19" s="17" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>28</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="9"/>
-      <c r="F15" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>181</v>
+      <c r="F15" s="42" t="s">
+        <v>180</v>
+      </c>
+      <c r="G15" s="43" t="s">
+        <v>185</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>26</v>
       </c>
       <c r="I15" s="25" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>13</v>
       </c>
       <c r="K15" s="9"/>
       <c r="L15" s="9"/>
-      <c r="M15" s="28" t="s">
+      <c r="M15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="N15" s="33"/>
-      <c r="O15" s="33"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="33"/>
-      <c r="R15" s="33"/>
-      <c r="S15" s="33"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
     </row>
     <row r="16" spans="1:19" s="17" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
@@ -1687,12 +1692,12 @@
       </c>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
-      <c r="N16" s="33"/>
-      <c r="O16" s="33"/>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="33"/>
-      <c r="R16" s="33"/>
-      <c r="S16" s="33"/>
+      <c r="N16" s="32"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="32"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="32"/>
+      <c r="S16" s="32"/>
     </row>
     <row r="17" spans="1:19" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
@@ -1717,12 +1722,12 @@
       </c>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
-      <c r="N17" s="31"/>
-      <c r="O17" s="31"/>
-      <c r="P17" s="31"/>
-      <c r="Q17" s="31"/>
-      <c r="R17" s="31"/>
-      <c r="S17" s="31"/>
+      <c r="N17" s="30"/>
+      <c r="O17" s="30"/>
+      <c r="P17" s="30"/>
+      <c r="Q17" s="30"/>
+      <c r="R17" s="30"/>
+      <c r="S17" s="30"/>
     </row>
     <row r="18" spans="1:19" s="17" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
@@ -1741,7 +1746,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="23"/>
       <c r="H18" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I18" s="8"/>
       <c r="J18" s="9" t="s">
@@ -1749,12 +1754,12 @@
       </c>
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
-      <c r="N18" s="31"/>
-      <c r="O18" s="31"/>
-      <c r="P18" s="31"/>
-      <c r="Q18" s="31"/>
-      <c r="R18" s="31"/>
-      <c r="S18" s="31"/>
+      <c r="N18" s="30"/>
+      <c r="O18" s="30"/>
+      <c r="P18" s="30"/>
+      <c r="Q18" s="30"/>
+      <c r="R18" s="30"/>
+      <c r="S18" s="30"/>
     </row>
     <row r="19" spans="1:19" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
@@ -1779,12 +1784,12 @@
       </c>
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
-      <c r="N19" s="31"/>
-      <c r="O19" s="31"/>
-      <c r="P19" s="31"/>
-      <c r="Q19" s="31"/>
-      <c r="R19" s="31"/>
-      <c r="S19" s="31"/>
+      <c r="N19" s="30"/>
+      <c r="O19" s="30"/>
+      <c r="P19" s="30"/>
+      <c r="Q19" s="30"/>
+      <c r="R19" s="30"/>
+      <c r="S19" s="30"/>
     </row>
     <row r="20" spans="1:19" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
@@ -1851,22 +1856,22 @@
       <c r="L22" s="11"/>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="42" t="s">
-        <v>184</v>
-      </c>
-      <c r="B23" s="42"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="42"/>
-      <c r="K23" s="42"/>
-      <c r="L23" s="42"/>
-      <c r="M23" s="42"/>
-      <c r="N23" s="42"/>
+      <c r="A23" s="41" t="s">
+        <v>170</v>
+      </c>
+      <c r="B23" s="41"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="41"/>
+      <c r="K23" s="41"/>
+      <c r="L23" s="41"/>
+      <c r="M23" s="41"/>
+      <c r="N23" s="41"/>
       <c r="O23"/>
       <c r="P23"/>
       <c r="Q23"/>
@@ -2692,12 +2697,12 @@
         <v>142</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="C2" t="s">
         <v>143</v>

--- a/SCH-STH/Impact assessments/Mali/2025/ml_sch_sth_impact_2501_2_child.xlsx
+++ b/SCH-STH/Impact assessments/Mali/2025/ml_sch_sth_impact_2501_2_child.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\SCH-STH\Impact assessments\Mali\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3710B4C-E8C7-4682-B5C2-4990079139DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC967F6-D688-4691-8CE0-423B048FE1B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -563,12 +563,6 @@
     <t>Veuillez enregistrer le code unique de l’enfant et des échantillons de labo </t>
   </si>
   <si>
-    <t>ml_sch_sth_impact_2501_2_child_v2_1</t>
-  </si>
-  <si>
-    <t>(2025 Jan) - 2. SCH/STH – Enrôlement V2.1</t>
-  </si>
-  <si>
     <t>ml_ia_e_250121</t>
   </si>
   <si>
@@ -584,9 +578,6 @@
     <t>not(selected(${C3}, ${p_code_id}))</t>
   </si>
   <si>
-    <t>concat(${p_recorder} , '_',  ${p_site_id} , '_',  ${p_sequential_code})</t>
-  </si>
-  <si>
     <t>p_sequential_code</t>
   </si>
   <si>
@@ -597,6 +588,15 @@
   </si>
   <si>
     <t>Cet identifiant a déjà été utilisé dans ce village.</t>
+  </si>
+  <si>
+    <t>ml_sch_sth_impact_2501_2_child_v3</t>
+  </si>
+  <si>
+    <t>(2025 Jan) - 2. SCH/STH – Enrôlement V3</t>
+  </si>
+  <si>
+    <t>concat(${p_site_id} , '_',  ${p_sequential_code})</t>
   </si>
 </sst>
 </file>
@@ -1445,7 +1445,7 @@
         <v>163</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C8" s="37" t="s">
         <v>164</v>
@@ -1504,7 +1504,7 @@
       <c r="L10" s="33"/>
       <c r="M10" s="33"/>
     </row>
-    <row r="11" spans="1:19" s="17" customFormat="1" ht="169.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" s="17" customFormat="1" ht="188.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>19</v>
       </c>
@@ -1560,15 +1560,15 @@
       <c r="R12" s="30"/>
       <c r="S12" s="31"/>
     </row>
-    <row r="13" spans="1:19" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" s="17" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="9"/>
@@ -1596,18 +1596,18 @@
         <v>29</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="9"/>
       <c r="F14" s="42" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>26</v>
@@ -1626,7 +1626,7 @@
       <c r="R14" s="32"/>
       <c r="S14" s="32"/>
     </row>
-    <row r="15" spans="1:19" s="17" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" s="17" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>28</v>
       </c>
@@ -1639,16 +1639,16 @@
       <c r="D15" s="10"/>
       <c r="E15" s="9"/>
       <c r="F15" s="42" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G15" s="43" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>26</v>
       </c>
       <c r="I15" s="25" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>13</v>
@@ -2683,7 +2683,7 @@
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.125" customWidth="1"/>
-    <col min="2" max="2" width="32.125" customWidth="1"/>
+    <col min="2" max="2" width="35.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -2697,12 +2697,12 @@
         <v>142</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="C2" t="s">
         <v>143</v>
